--- a/tests/scen_results_AGO2.xlsx
+++ b/tests/scen_results_AGO2.xlsx
@@ -27,7 +27,7 @@
     <t>2.0.11</t>
   </si>
   <si>
-    <t>2025-04-24</t>
+    <t>2025-04-28</t>
   </si>
   <si>
     <t>Scenario</t>
@@ -23818,34 +23818,34 @@
         <v>4212219.410027994</v>
       </c>
       <c r="G82" s="3">
-        <v>4262144.492062939</v>
+        <v>4238208.375984523</v>
       </c>
       <c r="H82" s="3">
-        <v>4317444.501416235</v>
+        <v>4268730.9962528</v>
       </c>
       <c r="I82" s="3">
-        <v>4375317.305816489</v>
+        <v>4300864.898670025</v>
       </c>
       <c r="J82" s="3">
-        <v>4437294.279713682</v>
+        <v>4335994.840180334</v>
       </c>
       <c r="K82" s="3">
-        <v>4501694.940340191</v>
+        <v>4372381.349151926</v>
       </c>
       <c r="L82" s="3">
-        <v>4569437.695280578</v>
+        <v>4411376.721499375</v>
       </c>
       <c r="M82" s="3">
-        <v>4639645.162146033</v>
+        <v>4452086.777320319</v>
       </c>
       <c r="N82" s="3">
-        <v>4708793.900967901</v>
+        <v>4491131.712348624</v>
       </c>
       <c r="O82" s="3">
-        <v>4778069.337999758</v>
+        <v>4529676.327589785</v>
       </c>
       <c r="P82" s="3">
-        <v>4846841.643099741</v>
+        <v>4567130.112100023</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -24026,34 +24026,34 @@
         <v>5884718.293421461</v>
       </c>
       <c r="G87" s="3">
-        <v>11595599.47454362</v>
+        <v>11530478.53190138</v>
       </c>
       <c r="H87" s="3">
-        <v>17460704.7446452</v>
+        <v>17263694.1381687</v>
       </c>
       <c r="I87" s="3">
-        <v>23164806.95665973</v>
+        <v>22770616.32214574</v>
       </c>
       <c r="J87" s="3">
-        <v>29367375.01863801</v>
+        <v>28696927.35384338</v>
       </c>
       <c r="K87" s="3">
-        <v>29794997.06917733</v>
+        <v>28939094.78278884</v>
       </c>
       <c r="L87" s="3">
-        <v>30244449.92030663</v>
+        <v>29198235.93966736</v>
       </c>
       <c r="M87" s="3">
-        <v>30709955.55400643</v>
+        <v>29468466.5486116</v>
       </c>
       <c r="N87" s="3">
-        <v>31168246.54063012</v>
+        <v>29727471.80631435</v>
       </c>
       <c r="O87" s="3">
-        <v>31627217.21562619</v>
+        <v>29983010.13487854</v>
       </c>
       <c r="P87" s="3">
-        <v>32082742.53366321</v>
+        <v>30231216.48272794</v>
       </c>
     </row>
     <row r="88" spans="1:16">

--- a/tests/scen_results_AGO2.xlsx
+++ b/tests/scen_results_AGO2.xlsx
@@ -27,7 +27,7 @@
     <t>2.0.11</t>
   </si>
   <si>
-    <t>2025-04-24</t>
+    <t>2025-04-28</t>
   </si>
   <si>
     <t>Scenario</t>
@@ -23226,34 +23226,34 @@
         <v>421221.9410027993</v>
       </c>
       <c r="G69" s="3">
-        <v>426203.19826347</v>
+        <v>424825.9276478021</v>
       </c>
       <c r="H69" s="3">
-        <v>431716.6884235952</v>
+        <v>429412.6572126428</v>
       </c>
       <c r="I69" s="3">
-        <v>437482.982882889</v>
+        <v>435128.1940316501</v>
       </c>
       <c r="J69" s="3">
-        <v>443655.8977601226</v>
+        <v>441496.7136813699</v>
       </c>
       <c r="K69" s="3">
-        <v>450067.938585561</v>
+        <v>448046.2082545989</v>
       </c>
       <c r="L69" s="3">
-        <v>456817.923281534</v>
+        <v>454934.8137642627</v>
       </c>
       <c r="M69" s="3">
-        <v>463818.471067033</v>
+        <v>462041.4907087638</v>
       </c>
       <c r="N69" s="3">
-        <v>470716.8404548462</v>
+        <v>468831.3761123036</v>
       </c>
       <c r="O69" s="3">
-        <v>477630.9800147941</v>
+        <v>475617.7683965765</v>
       </c>
       <c r="P69" s="3">
-        <v>484497.2700154034</v>
+        <v>482351.2465345509</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -23818,34 +23818,34 @@
         <v>4212219.410027994</v>
       </c>
       <c r="G82" s="3">
-        <v>4262144.492062939</v>
+        <v>4083699.47988556</v>
       </c>
       <c r="H82" s="3">
-        <v>4317444.501416235</v>
+        <v>4088764.424618563</v>
       </c>
       <c r="I82" s="3">
-        <v>4375317.305816489</v>
+        <v>4103597.627543734</v>
       </c>
       <c r="J82" s="3">
-        <v>4437294.279713682</v>
+        <v>4123369.226695425</v>
       </c>
       <c r="K82" s="3">
-        <v>4501694.940340191</v>
+        <v>4143583.244541653</v>
       </c>
       <c r="L82" s="3">
-        <v>4569437.695280578</v>
+        <v>4207344.501035417</v>
       </c>
       <c r="M82" s="3">
-        <v>4639645.162146033</v>
+        <v>4273083.505575663</v>
       </c>
       <c r="N82" s="3">
-        <v>4708793.900967901</v>
+        <v>4335957.997308251</v>
       </c>
       <c r="O82" s="3">
-        <v>4778069.337999758</v>
+        <v>4398864.879948239</v>
       </c>
       <c r="P82" s="3">
-        <v>4846841.643099741</v>
+        <v>4461255.566214114</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -24026,34 +24026,34 @@
         <v>5884718.293421461</v>
       </c>
       <c r="G87" s="3">
-        <v>11595599.47454362</v>
+        <v>10960755.22305375</v>
       </c>
       <c r="H87" s="3">
-        <v>17460704.7446452</v>
+        <v>15572613.23244935</v>
       </c>
       <c r="I87" s="3">
-        <v>23164806.95665973</v>
+        <v>19487245.97568408</v>
       </c>
       <c r="J87" s="3">
-        <v>29367375.01863801</v>
+        <v>23322984.61921107</v>
       </c>
       <c r="K87" s="3">
-        <v>29794997.06917733</v>
+        <v>22210006.69411445</v>
       </c>
       <c r="L87" s="3">
-        <v>30244449.92030663</v>
+        <v>22552580.43517987</v>
       </c>
       <c r="M87" s="3">
-        <v>30709955.55400643</v>
+        <v>22905456.98957662</v>
       </c>
       <c r="N87" s="3">
-        <v>31168246.54063012</v>
+        <v>23242559.37004323</v>
       </c>
       <c r="O87" s="3">
-        <v>31627217.21562619</v>
+        <v>23579953.63834275</v>
       </c>
       <c r="P87" s="3">
-        <v>32082742.53366321</v>
+        <v>23914444.00322239</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -24234,34 +24234,34 @@
         <v>5884718.293421461</v>
       </c>
       <c r="G92" s="3">
-        <v>11595430.81192187</v>
+        <v>11065310.85988447</v>
       </c>
       <c r="H92" s="3">
-        <v>17459968.09769737</v>
+        <v>15871284.20442493</v>
       </c>
       <c r="I92" s="3">
-        <v>23162944.26076956</v>
+        <v>20052478.21942293</v>
       </c>
       <c r="J92" s="3">
-        <v>29363655.94937871</v>
+        <v>24233593.56985438</v>
       </c>
       <c r="K92" s="3">
-        <v>29789676.72920444</v>
+        <v>23304629.25012399</v>
       </c>
       <c r="L92" s="3">
-        <v>30237724.66850416</v>
+        <v>23663891.57437608</v>
       </c>
       <c r="M92" s="3">
-        <v>30702052.62049105</v>
+        <v>24034139.45898903</v>
       </c>
       <c r="N92" s="3">
-        <v>31159376.02021847</v>
+        <v>24387426.15686936</v>
       </c>
       <c r="O92" s="3">
-        <v>31617558.10844445</v>
+        <v>24740660.50112538</v>
       </c>
       <c r="P92" s="3">
-        <v>32072438.82882728</v>
+        <v>25090984.70358322</v>
       </c>
     </row>
     <row r="93" spans="1:16">
